--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-del-maule.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-del-maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4404-177-CM26</t>
+          <t>1208066-112-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,43 +569,43 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>11180.61</v>
+        <v>8444.639999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3385-186-CM26</t>
+          <t>1079566-151-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,6 +630,860 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
+        <v>10096.77</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1079566-146-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>61.979.370-6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>7818.91</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1079566-147-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61.979.370-6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>IGMA CONSULTORES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>76.465.697-0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>9000.709999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2177-48-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>suria ltda</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>77.827.520-1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>5805.92</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2445-2835-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>16175.27</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1079566-171-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.979.370-6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>14867.29</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2292-693-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>IMPORTADORA FULLMUEBLES SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>77.351.814-9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>15360.57</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2177-59-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>suria ltda</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>77.827.520-1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>6887.42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2445-3090-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>10066.91</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1469-2229-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>7371.21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1389488-31-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.981.320-0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LOS ÁLAMOS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>5654.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4476-187-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.100.200-4</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MUEBLES SANTIAGO SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.369.344-9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>5799.46</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1079566-464-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.979.370-6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO PEDREROS CONCHA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>10.595.925-7</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>8347.959999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4404-177-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>11180.61</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3385-186-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.101.023-0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
         <v>7103.07</v>
       </c>
     </row>
